--- a/hotel_manager_forms/009_hotel_room_cleaning_checklist_form--hotel_manager_forms.xlsx
+++ b/hotel_manager_forms/009_hotel_room_cleaning_checklist_form--hotel_manager_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'bathroom_clean',_'label':_'clean',_'value':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Bathroom Clean', 'label': 'Clean', 'value': 'clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bathroom_not_clean',_'label':_'not_clean',_'value':_'not_clean'}</t>
+          <t>not_clean</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Bathroom Not Clean', 'label': 'Not Clean', 'value': 'not_clean'}</t>
+          <t>Not Clean</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'linen_clean',_'label':_'clean',_'value':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Linen Clean', 'label': 'Clean', 'value': 'clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'linen_not_clean',_'label':_'not_clean',_'value':_'not_clean'}</t>
+          <t>not_clean</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Linen Not Clean', 'label': 'Not Clean', 'value': 'not_clean'}</t>
+          <t>Not Clean</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'towels_provided',_'label':_'towels_provided',_'value':_'towels_provided'}</t>
+          <t>towels_provided</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Towels Provided', 'label': 'Towels Provided', 'value': 'towels_provided'}</t>
+          <t>Towels Provided</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'bedding_clean',_'label':_'clean',_'value':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Bedding Clean', 'label': 'Clean', 'value': 'clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bedding_not_clean',_'label':_'not_clean',_'value':_'not_clean'}</t>
+          <t>not_clean</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Bedding Not Clean', 'label': 'Not Clean', 'value': 'not_clean'}</t>
+          <t>Not Clean</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'furniture_clean',_'label':_'clean',_'value':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Furniture Clean', 'label': 'Clean', 'value': 'clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'furniture_not_clean',_'label':_'not_clean',_'value':_'not_clean'}</t>
+          <t>not_clean</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Furniture Not Clean', 'label': 'Not Clean', 'value': 'not_clean'}</t>
+          <t>Not Clean</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'carpet_clean',_'label':_'clean',_'value':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Carpet Clean', 'label': 'Clean', 'value': 'clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'carpet_not_clean',_'label':_'not_clean',_'value':_'not_clean'}</t>
+          <t>not_clean</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Carpet Not Clean', 'label': 'Not Clean', 'value': 'not_clean'}</t>
+          <t>Not Clean</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'floors_clean',_'label':_'clean',_'value':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Floors Clean', 'label': 'Clean', 'value': 'clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'floors_not_clean',_'label':_'not_clean',_'value':_'not_clean'}</t>
+          <t>not_clean</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Floors Not Clean', 'label': 'Not Clean', 'value': 'not_clean'}</t>
+          <t>Not Clean</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'electrical_equipment_clean',_'label':_'clean',_'value':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Electrical Equipment Clean', 'label': 'Clean', 'value': 'clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'electrical_equipment_not_clean',_'label':_'not_clean',_'value':_'not_clean'}</t>
+          <t>not_clean</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Electrical Equipment Not Clean', 'label': 'Not Clean', 'value': 'not_clean'}</t>
+          <t>Not Clean</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'kitchen_clean',_'label':_'clean',_'value':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Kitchen Clean', 'label': 'Clean', 'value': 'clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'kitchen_not_clean',_'label':_'not_clean',_'value':_'not_clean'}</t>
+          <t>not_clean</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Kitchen Not Clean', 'label': 'Not Clean', 'value': 'not_clean'}</t>
+          <t>Not Clean</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'laundry_clean',_'label':_'clean',_'value':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Laundry Clean', 'label': 'Clean', 'value': 'clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'laundry_not_clean',_'label':_'not_clean',_'value':_'not_clean'}</t>
+          <t>not_clean</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Laundry Not Clean', 'label': 'Not Clean', 'value': 'not_clean'}</t>
+          <t>Not Clean</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'miscellaneous_clean',_'label':_'clean',_'value':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Miscellaneous Clean', 'label': 'Clean', 'value': 'clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'miscellaneous_not_clean',_'label':_'not_clean',_'value':_'not_clean'}</t>
+          <t>not_clean</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Miscellaneous Not Clean', 'label': 'Not Clean', 'value': 'not_clean'}</t>
+          <t>Not Clean</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'general_info_1',_'label':_'general_info_1',_'value':_'general_info_1'}</t>
+          <t>general_info_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'General Info 1', 'label': 'General Info 1', 'value': 'general_info_1'}</t>
+          <t>General Info 1</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'general_info_2',_'label':_'general_info_2',_'value':_'general_info_2'}</t>
+          <t>general_info_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'General Info 2', 'label': 'General Info 2', 'value': 'general_info_2'}</t>
+          <t>General Info 2</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'specific_info_1',_'label':_'specific_info_1',_'value':_'specific_info_1'}</t>
+          <t>specific_info_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Specific Info 1', 'label': 'Specific Info 1', 'value': 'specific_info_1'}</t>
+          <t>Specific Info 1</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'specific_info_2',_'label':_'specific_info_2',_'value':_'specific_info_2'}</t>
+          <t>specific_info_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Specific Info 2', 'label': 'Specific Info 2', 'value': 'specific_info_2'}</t>
+          <t>Specific Info 2</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'specific_info_3_1',_'label':_'specific_info_3_1',_'value':_'specific_info_3_1'}</t>
+          <t>specific_info_3_1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Specific Info 3 1', 'label': 'Specific Info 3 1', 'value': 'specific_info_3_1'}</t>
+          <t>Specific Info 3 1</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'specific_info_3_2',_'label':_'specific_info_3_2',_'value':_'specific_info_3_2'}</t>
+          <t>specific_info_3_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Specific Info 3 2', 'label': 'Specific Info 3 2', 'value': 'specific_info_3_2'}</t>
+          <t>Specific Info 3 2</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'specific_info_4_1',_'label':_'specific_info_4_1',_'value':_'specific_info_4_1'}</t>
+          <t>specific_info_4_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Specific Info 4 1', 'label': 'Specific Info 4 1', 'value': 'specific_info_4_1'}</t>
+          <t>Specific Info 4 1</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'specific_info_4_2',_'label':_'specific_info_4_2',_'value':_'specific_info_4_2'}</t>
+          <t>specific_info_4_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Specific Info 4 2', 'label': 'Specific Info 4 2', 'value': 'specific_info_4_2'}</t>
+          <t>Specific Info 4 2</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'specific_info_5_1',_'label':_'specific_info_5_1',_'value':_'specific_info_5_1'}</t>
+          <t>specific_info_5_1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Specific Info 5 1', 'label': 'Specific Info 5 1', 'value': 'specific_info_5_1'}</t>
+          <t>Specific Info 5 1</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'specific_info_5_2',_'label':_'specific_info_5_2',_'value':_'specific_info_5_2'}</t>
+          <t>specific_info_5_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Specific Info 5 2', 'label': 'Specific Info 5 2', 'value': 'specific_info_5_2'}</t>
+          <t>Specific Info 5 2</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'specific_info_6_1',_'label':_'specific_info_6_1',_'value':_'specific_info_6_1'}</t>
+          <t>specific_info_6_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Specific Info 6 1', 'label': 'Specific Info 6 1', 'value': 'specific_info_6_1'}</t>
+          <t>Specific Info 6 1</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'specific_info_6_2',_'label':_'specific_info_6_2',_'value':_'specific_info_6_2'}</t>
+          <t>specific_info_6_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Specific Info 6 2', 'label': 'Specific Info 6 2', 'value': 'specific_info_6_2'}</t>
+          <t>Specific Info 6 2</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'specific_info_7_1',_'label':_'specific_info_7_1',_'value':_'specific_info_7_1'}</t>
+          <t>specific_info_7_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Specific Info 7 1', 'label': 'Specific Info 7 1', 'value': 'specific_info_7_1'}</t>
+          <t>Specific Info 7 1</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'specific_info_7_2',_'label':_'specific_info_7_2',_'value':_'specific_info_7_2'}</t>
+          <t>specific_info_7_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Specific Info 7 2', 'label': 'Specific Info 7 2', 'value': 'specific_info_7_2'}</t>
+          <t>Specific Info 7 2</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'specific_info_8_1',_'label':_'specific_info_8_1',_'value':_'specific_info_8_1'}</t>
+          <t>specific_info_8_1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Specific Info 8 1', 'label': 'Specific Info 8 1', 'value': 'specific_info_8_1'}</t>
+          <t>Specific Info 8 1</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'specific_info_8_2',_'label':_'specific_info_8_2',_'value':_'specific_info_8_2'}</t>
+          <t>specific_info_8_2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Specific Info 8 2', 'label': 'Specific Info 8 2', 'value': 'specific_info_8_2'}</t>
+          <t>Specific Info 8 2</t>
         </is>
       </c>
     </row>
